--- a/LISTAS_ORDENADAS/MI/Tornillos Pitones Arandelas Tuercas/GANCHO J.xlsx
+++ b/LISTAS_ORDENADAS/MI/Tornillos Pitones Arandelas Tuercas/GANCHO J.xlsx
@@ -778,7 +778,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45208.55636324279</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
@@ -885,20 +885,6 @@
       </c>
       <c r="C11" s="10" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26" ht="13.5" customHeight="1" s="25">
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
@@ -1203,7 +1189,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
     <row r="42" ht="13.5" customHeight="1" s="25">
       <c r="B42" s="8" t="inlineStr">
         <is>
@@ -1213,17 +1198,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B28:C28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
